--- a/Team-Data/2009-10/2-23-2009-10.xlsx
+++ b/Team-Data/2009-10/2-23-2009-10.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,43 +728,43 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F2" t="n">
         <v>20</v>
       </c>
       <c r="G2" t="n">
-        <v>0.63</v>
+        <v>0.636</v>
       </c>
       <c r="H2" t="n">
         <v>48.3</v>
       </c>
       <c r="I2" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J2" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="K2" t="n">
-        <v>0.465</v>
+        <v>0.466</v>
       </c>
       <c r="L2" t="n">
         <v>6.4</v>
       </c>
       <c r="M2" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.352</v>
+        <v>0.355</v>
       </c>
       <c r="O2" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P2" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="Q2" t="n">
         <v>0.758</v>
@@ -709,16 +776,16 @@
         <v>29.5</v>
       </c>
       <c r="T2" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U2" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V2" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="W2" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X2" t="n">
         <v>5.2</v>
@@ -727,34 +794,34 @@
         <v>4.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>101.1</v>
+        <v>101.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
       </c>
       <c r="AF2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG2" t="n">
         <v>7</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>8</v>
       </c>
       <c r="AH2" t="n">
         <v>19</v>
       </c>
       <c r="AI2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ2" t="n">
         <v>13</v>
@@ -763,22 +830,22 @@
         <v>10</v>
       </c>
       <c r="AL2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR2" t="n">
         <v>12</v>
@@ -790,13 +857,13 @@
         <v>23</v>
       </c>
       <c r="AU2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AV2" t="n">
         <v>1</v>
       </c>
       <c r="AW2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AX2" t="n">
         <v>11</v>
@@ -808,10 +875,10 @@
         <v>8</v>
       </c>
       <c r="BA2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BC2" t="n">
         <v>7</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -843,37 +910,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
         <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>0.642</v>
+        <v>0.648</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
       </c>
       <c r="I3" t="n">
-        <v>37.1</v>
+        <v>36.8</v>
       </c>
       <c r="J3" t="n">
-        <v>76.3</v>
+        <v>76.2</v>
       </c>
       <c r="K3" t="n">
-        <v>0.486</v>
+        <v>0.483</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="M3" t="n">
-        <v>17.6</v>
+        <v>17.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.341</v>
+        <v>0.345</v>
       </c>
       <c r="O3" t="n">
         <v>18.8</v>
@@ -882,7 +949,7 @@
         <v>25.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.734</v>
+        <v>0.736</v>
       </c>
       <c r="R3" t="n">
         <v>8.6</v>
@@ -891,34 +958,34 @@
         <v>30.2</v>
       </c>
       <c r="T3" t="n">
-        <v>38.7</v>
+        <v>38.9</v>
       </c>
       <c r="U3" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="V3" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W3" t="n">
         <v>8.6</v>
       </c>
       <c r="X3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y3" t="n">
         <v>5</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="AC3" t="n">
         <v>4.9</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>4.4</v>
       </c>
       <c r="AD3" t="n">
         <v>27</v>
@@ -930,28 +997,28 @@
         <v>3</v>
       </c>
       <c r="AG3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AH3" t="n">
         <v>17</v>
       </c>
       <c r="AI3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
       </c>
       <c r="AK3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL3" t="n">
         <v>18</v>
       </c>
       <c r="AM3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN3" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AO3" t="n">
         <v>13</v>
@@ -966,7 +1033,7 @@
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT3" t="n">
         <v>29</v>
@@ -981,22 +1048,22 @@
         <v>2</v>
       </c>
       <c r="AX3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ3" t="n">
         <v>22</v>
       </c>
       <c r="BA3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -1025,61 +1092,61 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E4" t="n">
         <v>27</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5</v>
+        <v>0.491</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>35.1</v>
+        <v>34.9</v>
       </c>
       <c r="J4" t="n">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.455</v>
+        <v>0.452</v>
       </c>
       <c r="L4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="M4" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="N4" t="n">
-        <v>0.345</v>
+        <v>0.341</v>
       </c>
       <c r="O4" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="P4" t="n">
         <v>26.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.747</v>
+        <v>0.743</v>
       </c>
       <c r="R4" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S4" t="n">
         <v>30</v>
       </c>
       <c r="T4" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="U4" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="V4" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="W4" t="n">
         <v>7.7</v>
@@ -1091,28 +1158,28 @@
         <v>6.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA4" t="n">
         <v>21.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AE4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF4" t="n">
         <v>18</v>
       </c>
-      <c r="AF4" t="n">
-        <v>16</v>
-      </c>
       <c r="AG4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH4" t="n">
         <v>10</v>
@@ -1124,22 +1191,22 @@
         <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AL4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM4" t="n">
         <v>19</v>
       </c>
       <c r="AN4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AO4" t="n">
         <v>6</v>
       </c>
       <c r="AP4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AQ4" t="n">
         <v>19</v>
@@ -1157,7 +1224,7 @@
         <v>22</v>
       </c>
       <c r="AV4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW4" t="n">
         <v>8</v>
@@ -1172,13 +1239,13 @@
         <v>4</v>
       </c>
       <c r="BA4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -1285,13 +1352,13 @@
         <v>-1.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE5" t="n">
         <v>15</v>
       </c>
       <c r="AF5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG5" t="n">
         <v>15</v>
@@ -1309,25 +1376,25 @@
         <v>25</v>
       </c>
       <c r="AL5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM5" t="n">
         <v>30</v>
       </c>
       <c r="AN5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS5" t="n">
         <v>2</v>
@@ -1342,7 +1409,7 @@
         <v>17</v>
       </c>
       <c r="AW5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AX5" t="n">
         <v>1</v>
@@ -1354,7 +1421,7 @@
         <v>2</v>
       </c>
       <c r="BA5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB5" t="n">
         <v>25</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -1389,85 +1456,85 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>0.786</v>
+        <v>0.754</v>
       </c>
       <c r="H6" t="n">
         <v>48.3</v>
       </c>
       <c r="I6" t="n">
-        <v>37.8</v>
+        <v>37.4</v>
       </c>
       <c r="J6" t="n">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.489</v>
+        <v>0.485</v>
       </c>
       <c r="L6" t="n">
         <v>7.6</v>
       </c>
       <c r="M6" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0.398</v>
+        <v>0.399</v>
       </c>
       <c r="O6" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="P6" t="n">
-        <v>26.2</v>
+        <v>26.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.726</v>
+        <v>0.725</v>
       </c>
       <c r="R6" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="S6" t="n">
         <v>32.6</v>
       </c>
       <c r="T6" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U6" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="V6" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W6" t="n">
         <v>6.8</v>
       </c>
       <c r="X6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.8</v>
+        <v>20.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.5</v>
+        <v>20.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>102.1</v>
+        <v>101.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1503,10 +1570,10 @@
         <v>11</v>
       </c>
       <c r="AP6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR6" t="n">
         <v>28</v>
@@ -1518,31 +1585,31 @@
         <v>15</v>
       </c>
       <c r="AU6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AV6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AW6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AX6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC6" t="n">
         <v>2</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -1571,28 +1638,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E7" t="n">
         <v>36</v>
       </c>
       <c r="F7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7" t="n">
-        <v>0.643</v>
+        <v>0.632</v>
       </c>
       <c r="H7" t="n">
         <v>48.5</v>
       </c>
       <c r="I7" t="n">
-        <v>37.8</v>
+        <v>37.6</v>
       </c>
       <c r="J7" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L7" t="n">
         <v>6.4</v>
@@ -1601,28 +1668,28 @@
         <v>17.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0.361</v>
+        <v>0.359</v>
       </c>
       <c r="O7" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="P7" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="R7" t="n">
         <v>10.4</v>
       </c>
       <c r="S7" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T7" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U7" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="V7" t="n">
         <v>13</v>
@@ -1631,7 +1698,7 @@
         <v>7.3</v>
       </c>
       <c r="X7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y7" t="n">
         <v>4.3</v>
@@ -1640,28 +1707,28 @@
         <v>19.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>100.9</v>
+        <v>100.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AD7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE7" t="n">
         <v>5</v>
       </c>
-      <c r="AE7" t="n">
-        <v>4</v>
-      </c>
       <c r="AF7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AH7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AI7" t="n">
         <v>14</v>
@@ -1670,16 +1737,16 @@
         <v>15</v>
       </c>
       <c r="AK7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AL7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AM7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AO7" t="n">
         <v>12</v>
@@ -1697,19 +1764,19 @@
         <v>7</v>
       </c>
       <c r="AT7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU7" t="n">
         <v>3</v>
       </c>
       <c r="AV7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AY7" t="n">
         <v>5</v>
@@ -1718,13 +1785,13 @@
         <v>1</v>
       </c>
       <c r="BA7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -1753,34 +1820,34 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F8" t="n">
         <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>0.655</v>
+        <v>0.661</v>
       </c>
       <c r="H8" t="n">
         <v>48.4</v>
       </c>
       <c r="I8" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J8" t="n">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="K8" t="n">
-        <v>0.471</v>
+        <v>0.472</v>
       </c>
       <c r="L8" t="n">
         <v>6.6</v>
       </c>
       <c r="M8" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="N8" t="n">
         <v>0.378</v>
@@ -1795,7 +1862,7 @@
         <v>0.775</v>
       </c>
       <c r="R8" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S8" t="n">
         <v>30.6</v>
@@ -1807,10 +1874,10 @@
         <v>21.1</v>
       </c>
       <c r="V8" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W8" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="X8" t="n">
         <v>5</v>
@@ -1819,19 +1886,19 @@
         <v>5.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AA8" t="n">
         <v>24.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>107.3</v>
+        <v>107.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AE8" t="n">
         <v>4</v>
@@ -1843,10 +1910,10 @@
         <v>4</v>
       </c>
       <c r="AH8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ8" t="n">
         <v>18</v>
@@ -1870,13 +1937,13 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR8" t="n">
         <v>19</v>
       </c>
       <c r="AS8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT8" t="n">
         <v>18</v>
@@ -1885,13 +1952,13 @@
         <v>16</v>
       </c>
       <c r="AV8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW8" t="n">
         <v>3</v>
       </c>
       <c r="AX8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AY8" t="n">
         <v>24</v>
@@ -1903,7 +1970,7 @@
         <v>1</v>
       </c>
       <c r="BB8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC8" t="n">
         <v>5</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -1950,31 +2017,31 @@
         <v>48.3</v>
       </c>
       <c r="I9" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="J9" t="n">
-        <v>80.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.438</v>
+        <v>0.436</v>
       </c>
       <c r="L9" t="n">
         <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="N9" t="n">
-        <v>0.292</v>
+        <v>0.293</v>
       </c>
       <c r="O9" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="P9" t="n">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.727</v>
+        <v>0.726</v>
       </c>
       <c r="R9" t="n">
         <v>13.1</v>
@@ -1983,16 +2050,16 @@
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U9" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="V9" t="n">
         <v>13.8</v>
       </c>
       <c r="W9" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X9" t="n">
         <v>3.9</v>
@@ -2004,16 +2071,16 @@
         <v>22.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>92.3</v>
+        <v>92.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>-4.8</v>
+        <v>-4.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE9" t="n">
         <v>23</v>
@@ -2022,10 +2089,10 @@
         <v>24</v>
       </c>
       <c r="AG9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI9" t="n">
         <v>28</v>
@@ -2034,19 +2101,19 @@
         <v>19</v>
       </c>
       <c r="AK9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AM9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AN9" t="n">
         <v>30</v>
       </c>
       <c r="AO9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP9" t="n">
         <v>14</v>
@@ -2061,7 +2128,7 @@
         <v>30</v>
       </c>
       <c r="AT9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU9" t="n">
         <v>28</v>
@@ -2070,13 +2137,13 @@
         <v>10</v>
       </c>
       <c r="AW9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AX9" t="n">
         <v>28</v>
       </c>
       <c r="AY9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ9" t="n">
         <v>27</v>
@@ -2088,7 +2155,7 @@
         <v>29</v>
       </c>
       <c r="BC9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -2132,22 +2199,22 @@
         <v>48.2</v>
       </c>
       <c r="I10" t="n">
-        <v>40</v>
+        <v>40.2</v>
       </c>
       <c r="J10" t="n">
-        <v>85.5</v>
+        <v>85.3</v>
       </c>
       <c r="K10" t="n">
-        <v>0.469</v>
+        <v>0.471</v>
       </c>
       <c r="L10" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="M10" t="n">
-        <v>18.5</v>
+        <v>18.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0.361</v>
+        <v>0.36</v>
       </c>
       <c r="O10" t="n">
         <v>20.5</v>
@@ -2156,28 +2223,28 @@
         <v>26.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.778</v>
+        <v>0.776</v>
       </c>
       <c r="R10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T10" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="U10" t="n">
         <v>21.9</v>
       </c>
       <c r="V10" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="W10" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="X10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y10" t="n">
         <v>5.1</v>
@@ -2189,13 +2256,13 @@
         <v>21.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>107.3</v>
+        <v>107.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE10" t="n">
         <v>28</v>
@@ -2207,7 +2274,7 @@
         <v>28</v>
       </c>
       <c r="AH10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2216,22 +2283,22 @@
         <v>2</v>
       </c>
       <c r="AK10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN10" t="n">
         <v>9</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>7</v>
       </c>
       <c r="AO10" t="n">
         <v>4</v>
       </c>
       <c r="AP10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ10" t="n">
         <v>5</v>
@@ -2243,7 +2310,7 @@
         <v>26</v>
       </c>
       <c r="AT10" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AU10" t="n">
         <v>8</v>
@@ -2258,16 +2325,16 @@
         <v>24</v>
       </c>
       <c r="AY10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ10" t="n">
         <v>29</v>
       </c>
       <c r="BA10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC10" t="n">
         <v>23</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -2299,28 +2366,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E11" t="n">
+        <v>28</v>
+      </c>
+      <c r="F11" t="n">
         <v>27</v>
-      </c>
-      <c r="F11" t="n">
-        <v>26</v>
       </c>
       <c r="G11" t="n">
         <v>0.509</v>
       </c>
       <c r="H11" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="I11" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J11" t="n">
         <v>84.59999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L11" t="n">
         <v>7.9</v>
@@ -2329,61 +2396,61 @@
         <v>22.7</v>
       </c>
       <c r="N11" t="n">
-        <v>0.346</v>
+        <v>0.347</v>
       </c>
       <c r="O11" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="P11" t="n">
         <v>24.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="R11" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="S11" t="n">
-        <v>30.7</v>
+        <v>30.5</v>
       </c>
       <c r="T11" t="n">
-        <v>43</v>
+        <v>42.7</v>
       </c>
       <c r="U11" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V11" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="X11" t="n">
         <v>4</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>101.1</v>
+        <v>101</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="AE11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG11" t="n">
         <v>16</v>
@@ -2407,25 +2474,25 @@
         <v>3</v>
       </c>
       <c r="AN11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AO11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP11" t="n">
         <v>16</v>
       </c>
       <c r="AQ11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AR11" t="n">
         <v>3</v>
       </c>
       <c r="AS11" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AT11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU11" t="n">
         <v>14</v>
@@ -2434,7 +2501,7 @@
         <v>18</v>
       </c>
       <c r="AW11" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AX11" t="n">
         <v>27</v>
@@ -2449,7 +2516,7 @@
         <v>5</v>
       </c>
       <c r="BB11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC11" t="n">
         <v>16</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -2481,37 +2548,37 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E12" t="n">
         <v>19</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G12" t="n">
-        <v>0.345</v>
+        <v>0.339</v>
       </c>
       <c r="H12" t="n">
         <v>48</v>
       </c>
       <c r="I12" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J12" t="n">
-        <v>84</v>
+        <v>83.8</v>
       </c>
       <c r="K12" t="n">
-        <v>0.435</v>
+        <v>0.437</v>
       </c>
       <c r="L12" t="n">
         <v>7.4</v>
       </c>
       <c r="M12" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.327</v>
+        <v>0.331</v>
       </c>
       <c r="O12" t="n">
         <v>18.5</v>
@@ -2520,25 +2587,25 @@
         <v>23.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.773</v>
+        <v>0.775</v>
       </c>
       <c r="R12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S12" t="n">
         <v>32.6</v>
       </c>
       <c r="T12" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U12" t="n">
         <v>20.3</v>
       </c>
       <c r="V12" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W12" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X12" t="n">
         <v>5.8</v>
@@ -2547,28 +2614,28 @@
         <v>5.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>98.90000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC12" t="n">
-        <v>-4.6</v>
+        <v>-4.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AE12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH12" t="n">
         <v>29</v>
@@ -2577,10 +2644,10 @@
         <v>23</v>
       </c>
       <c r="AJ12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AK12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL12" t="n">
         <v>8</v>
@@ -2598,7 +2665,7 @@
         <v>20</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AR12" t="n">
         <v>26</v>
@@ -2610,19 +2677,19 @@
         <v>11</v>
       </c>
       <c r="AU12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AV12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX12" t="n">
         <v>3</v>
       </c>
       <c r="AY12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ12" t="n">
         <v>30</v>
@@ -2631,10 +2698,10 @@
         <v>16</v>
       </c>
       <c r="BB12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -2663,64 +2730,64 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E13" t="n">
         <v>23</v>
       </c>
       <c r="F13" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G13" t="n">
-        <v>0.426</v>
+        <v>0.411</v>
       </c>
       <c r="H13" t="n">
         <v>48.1</v>
       </c>
       <c r="I13" t="n">
-        <v>36.2</v>
+        <v>36.4</v>
       </c>
       <c r="J13" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.457</v>
+        <v>0.459</v>
       </c>
       <c r="L13" t="n">
         <v>5.2</v>
       </c>
       <c r="M13" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="N13" t="n">
         <v>0.322</v>
       </c>
       <c r="O13" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="P13" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.727</v>
+        <v>0.723</v>
       </c>
       <c r="R13" t="n">
         <v>11.1</v>
       </c>
       <c r="S13" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T13" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U13" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="V13" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W13" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X13" t="n">
         <v>5.9</v>
@@ -2729,19 +2796,19 @@
         <v>4.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>95.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC13" t="n">
         <v>-4.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="AE13" t="n">
         <v>21</v>
@@ -2762,13 +2829,13 @@
         <v>23</v>
       </c>
       <c r="AK13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL13" t="n">
         <v>23</v>
       </c>
       <c r="AM13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AN13" t="n">
         <v>28</v>
@@ -2777,43 +2844,43 @@
         <v>26</v>
       </c>
       <c r="AP13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AQ13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AR13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS13" t="n">
         <v>24</v>
       </c>
       <c r="AT13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
       </c>
       <c r="AY13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AZ13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC13" t="n">
         <v>25</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -2860,13 +2927,13 @@
         <v>48.4</v>
       </c>
       <c r="I14" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="J14" t="n">
-        <v>84.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="K14" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L14" t="n">
         <v>6.6</v>
@@ -2875,31 +2942,31 @@
         <v>19</v>
       </c>
       <c r="N14" t="n">
-        <v>0.347</v>
+        <v>0.345</v>
       </c>
       <c r="O14" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="P14" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R14" t="n">
-        <v>11.5</v>
+        <v>11.7</v>
       </c>
       <c r="S14" t="n">
         <v>33.3</v>
       </c>
       <c r="T14" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
       <c r="U14" t="n">
         <v>21.5</v>
       </c>
       <c r="V14" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="W14" t="n">
         <v>7.5</v>
@@ -2911,25 +2978,25 @@
         <v>4.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB14" t="n">
         <v>102.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
         <v>2</v>
@@ -2953,19 +3020,19 @@
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AO14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AS14" t="n">
         <v>3</v>
@@ -2986,7 +3053,7 @@
         <v>19</v>
       </c>
       <c r="AY14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ14" t="n">
         <v>3</v>
@@ -2998,7 +3065,7 @@
         <v>5</v>
       </c>
       <c r="BC14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -3042,13 +3109,13 @@
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>39.6</v>
+        <v>39.3</v>
       </c>
       <c r="J15" t="n">
-        <v>84.09999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.47</v>
+        <v>0.469</v>
       </c>
       <c r="L15" t="n">
         <v>4.2</v>
@@ -3057,76 +3124,76 @@
         <v>12.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0.34</v>
+        <v>0.337</v>
       </c>
       <c r="O15" t="n">
         <v>19.3</v>
       </c>
       <c r="P15" t="n">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.74</v>
+        <v>0.738</v>
       </c>
       <c r="R15" t="n">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="S15" t="n">
         <v>30.1</v>
       </c>
       <c r="T15" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="U15" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="V15" t="n">
         <v>15.2</v>
       </c>
       <c r="W15" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X15" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="n">
         <v>5.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.6</v>
+        <v>102.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.7</v>
+        <v>-1.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG15" t="n">
         <v>16</v>
       </c>
-      <c r="AF15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>17</v>
-      </c>
       <c r="AH15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI15" t="n">
         <v>3</v>
       </c>
       <c r="AJ15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL15" t="n">
         <v>27</v>
@@ -3135,7 +3202,7 @@
         <v>29</v>
       </c>
       <c r="AN15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO15" t="n">
         <v>10</v>
@@ -3144,7 +3211,7 @@
         <v>9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AR15" t="n">
         <v>2</v>
@@ -3159,28 +3226,28 @@
         <v>25</v>
       </c>
       <c r="AV15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW15" t="n">
         <v>7</v>
       </c>
       <c r="AX15" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AY15" t="n">
         <v>28</v>
       </c>
       <c r="AZ15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB15" t="n">
         <v>6</v>
       </c>
       <c r="BC15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -3212,34 +3279,34 @@
         <v>57</v>
       </c>
       <c r="E16" t="n">
+        <v>29</v>
+      </c>
+      <c r="F16" t="n">
         <v>28</v>
       </c>
-      <c r="F16" t="n">
-        <v>29</v>
-      </c>
       <c r="G16" t="n">
-        <v>0.491</v>
+        <v>0.509</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>36.3</v>
+        <v>36.5</v>
       </c>
       <c r="J16" t="n">
-        <v>80</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.453</v>
+        <v>0.456</v>
       </c>
       <c r="L16" t="n">
         <v>5.9</v>
       </c>
       <c r="M16" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0.345</v>
+        <v>0.346</v>
       </c>
       <c r="O16" t="n">
         <v>17.6</v>
@@ -3248,58 +3315,58 @@
         <v>23.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.75</v>
+        <v>0.749</v>
       </c>
       <c r="R16" t="n">
         <v>10.8</v>
       </c>
       <c r="S16" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="T16" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="U16" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="V16" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="W16" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X16" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y16" t="n">
         <v>4.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA16" t="n">
         <v>19.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>96.09999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AD16" t="n">
         <v>2</v>
       </c>
       <c r="AE16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
         <v>24</v>
@@ -3308,31 +3375,31 @@
         <v>22</v>
       </c>
       <c r="AK16" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AL16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM16" t="n">
         <v>20</v>
       </c>
       <c r="AN16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO16" t="n">
         <v>25</v>
       </c>
       <c r="AP16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ16" t="n">
         <v>18</v>
       </c>
       <c r="AR16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT16" t="n">
         <v>17</v>
@@ -3341,16 +3408,16 @@
         <v>26</v>
       </c>
       <c r="AV16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AX16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ16" t="n">
         <v>21</v>
@@ -3362,7 +3429,7 @@
         <v>26</v>
       </c>
       <c r="BC16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -3469,19 +3536,19 @@
         <v>0.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF17" t="n">
         <v>18</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AG17" t="n">
         <v>19</v>
       </c>
-      <c r="AG17" t="n">
-        <v>20</v>
-      </c>
       <c r="AH17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI17" t="n">
         <v>17</v>
@@ -3499,7 +3566,7 @@
         <v>6</v>
       </c>
       <c r="AN17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AO17" t="n">
         <v>30</v>
@@ -3511,13 +3578,13 @@
         <v>22</v>
       </c>
       <c r="AR17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT17" t="n">
         <v>5</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>6</v>
       </c>
       <c r="AU17" t="n">
         <v>15</v>
@@ -3526,7 +3593,7 @@
         <v>8</v>
       </c>
       <c r="AW17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX17" t="n">
         <v>23</v>
@@ -3538,10 +3605,10 @@
         <v>26</v>
       </c>
       <c r="BA17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC17" t="n">
         <v>15</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -3591,34 +3658,34 @@
         <v>38.1</v>
       </c>
       <c r="J18" t="n">
-        <v>84.90000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L18" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="M18" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.342</v>
+        <v>0.336</v>
       </c>
       <c r="O18" t="n">
-        <v>16.9</v>
+        <v>17.1</v>
       </c>
       <c r="P18" t="n">
-        <v>22.9</v>
+        <v>23.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.738</v>
+        <v>0.737</v>
       </c>
       <c r="R18" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S18" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="T18" t="n">
         <v>43.4</v>
@@ -3627,22 +3694,22 @@
         <v>19.7</v>
       </c>
       <c r="V18" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="W18" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X18" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Y18" t="n">
         <v>5.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="AB18" t="n">
         <v>97.90000000000001</v>
@@ -3675,28 +3742,28 @@
         <v>23</v>
       </c>
       <c r="AL18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AN18" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AO18" t="n">
         <v>27</v>
       </c>
       <c r="AP18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AS18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT18" t="n">
         <v>4</v>
@@ -3717,10 +3784,10 @@
         <v>25</v>
       </c>
       <c r="AZ18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB18" t="n">
         <v>21</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -3773,55 +3840,55 @@
         <v>33.7</v>
       </c>
       <c r="J19" t="n">
-        <v>79</v>
+        <v>79.2</v>
       </c>
       <c r="K19" t="n">
-        <v>0.426</v>
+        <v>0.425</v>
       </c>
       <c r="L19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="M19" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0.303</v>
+        <v>0.296</v>
       </c>
       <c r="O19" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P19" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="Q19" t="n">
         <v>0.774</v>
       </c>
       <c r="R19" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="S19" t="n">
-        <v>28.1</v>
+        <v>28.3</v>
       </c>
       <c r="T19" t="n">
-        <v>38.7</v>
+        <v>39.1</v>
       </c>
       <c r="U19" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="V19" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="W19" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA19" t="n">
         <v>20</v>
@@ -3830,10 +3897,10 @@
         <v>90</v>
       </c>
       <c r="AC19" t="n">
-        <v>-11.3</v>
+        <v>-11.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE19" t="n">
         <v>30</v>
@@ -3869,10 +3936,10 @@
         <v>14</v>
       </c>
       <c r="AP19" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR19" t="n">
         <v>18</v>
@@ -3881,7 +3948,7 @@
         <v>29</v>
       </c>
       <c r="AT19" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AU19" t="n">
         <v>30</v>
@@ -3893,16 +3960,16 @@
         <v>12</v>
       </c>
       <c r="AX19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY19" t="n">
         <v>21</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>22</v>
       </c>
       <c r="AZ19" t="n">
         <v>14</v>
       </c>
       <c r="BA19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB19" t="n">
         <v>30</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -3961,31 +4028,31 @@
         <v>0.455</v>
       </c>
       <c r="L20" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="M20" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="N20" t="n">
-        <v>0.36</v>
+        <v>0.363</v>
       </c>
       <c r="O20" t="n">
         <v>16.2</v>
       </c>
       <c r="P20" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.79</v>
+        <v>0.784</v>
       </c>
       <c r="R20" t="n">
         <v>10.5</v>
       </c>
       <c r="S20" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T20" t="n">
-        <v>41.1</v>
+        <v>40.9</v>
       </c>
       <c r="U20" t="n">
         <v>22.1</v>
@@ -3997,28 +4064,28 @@
         <v>7.6</v>
       </c>
       <c r="X20" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z20" t="n">
         <v>19.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB20" t="n">
         <v>100</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="AD20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF20" t="n">
         <v>13</v>
@@ -4036,7 +4103,7 @@
         <v>10</v>
       </c>
       <c r="AK20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL20" t="n">
         <v>7</v>
@@ -4045,7 +4112,7 @@
         <v>7</v>
       </c>
       <c r="AN20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AO20" t="n">
         <v>28</v>
@@ -4054,7 +4121,7 @@
         <v>29</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR20" t="n">
         <v>20</v>
@@ -4066,7 +4133,7 @@
         <v>22</v>
       </c>
       <c r="AU20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV20" t="n">
         <v>6</v>
@@ -4078,19 +4145,19 @@
         <v>29</v>
       </c>
       <c r="AY20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ20" t="n">
         <v>5</v>
       </c>
       <c r="BA20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB20" t="n">
         <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -4134,46 +4201,46 @@
         <v>48.6</v>
       </c>
       <c r="I21" t="n">
-        <v>38.1</v>
+        <v>37.9</v>
       </c>
       <c r="J21" t="n">
-        <v>84.2</v>
+        <v>84.3</v>
       </c>
       <c r="K21" t="n">
-        <v>0.452</v>
+        <v>0.45</v>
       </c>
       <c r="L21" t="n">
         <v>8.9</v>
       </c>
       <c r="M21" t="n">
-        <v>26.2</v>
+        <v>26.4</v>
       </c>
       <c r="N21" t="n">
-        <v>0.339</v>
+        <v>0.337</v>
       </c>
       <c r="O21" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="P21" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.771</v>
+        <v>0.773</v>
       </c>
       <c r="R21" t="n">
         <v>10.3</v>
       </c>
       <c r="S21" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T21" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="U21" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V21" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W21" t="n">
         <v>7.3</v>
@@ -4182,7 +4249,7 @@
         <v>4.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z21" t="n">
         <v>19.9</v>
@@ -4191,16 +4258,16 @@
         <v>19.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>101.1</v>
+        <v>100.9</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.8</v>
+        <v>-3.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF21" t="n">
         <v>25</v>
@@ -4209,10 +4276,10 @@
         <v>25</v>
       </c>
       <c r="AH21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AJ21" t="n">
         <v>6</v>
@@ -4227,7 +4294,7 @@
         <v>2</v>
       </c>
       <c r="AN21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4236,7 +4303,7 @@
         <v>28</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
         <v>22</v>
@@ -4245,31 +4312,31 @@
         <v>19</v>
       </c>
       <c r="AT21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AV21" t="n">
         <v>11</v>
       </c>
       <c r="AW21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX21" t="n">
         <v>25</v>
       </c>
       <c r="AY21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BC21" t="n">
         <v>22</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -4304,13 +4371,13 @@
         <v>54</v>
       </c>
       <c r="E22" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G22" t="n">
-        <v>0.593</v>
+        <v>0.611</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4319,52 +4386,52 @@
         <v>36.6</v>
       </c>
       <c r="J22" t="n">
-        <v>80.40000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="K22" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L22" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="M22" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="N22" t="n">
-        <v>0.338</v>
+        <v>0.344</v>
       </c>
       <c r="O22" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="P22" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.796</v>
+        <v>0.794</v>
       </c>
       <c r="R22" t="n">
         <v>11.5</v>
       </c>
       <c r="S22" t="n">
-        <v>32</v>
+        <v>32.2</v>
       </c>
       <c r="T22" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
       <c r="U22" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="V22" t="n">
         <v>15.4</v>
       </c>
       <c r="W22" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X22" t="n">
         <v>5.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z22" t="n">
         <v>21.1</v>
@@ -4376,22 +4443,22 @@
         <v>99.09999999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AE22" t="n">
         <v>10</v>
       </c>
       <c r="AF22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG22" t="n">
         <v>9</v>
       </c>
-      <c r="AG22" t="n">
-        <v>10</v>
-      </c>
       <c r="AH22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI22" t="n">
         <v>22</v>
@@ -4400,7 +4467,7 @@
         <v>20</v>
       </c>
       <c r="AK22" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AL22" t="n">
         <v>24</v>
@@ -4409,19 +4476,19 @@
         <v>24</v>
       </c>
       <c r="AN22" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AO22" t="n">
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AQ22" t="n">
         <v>2</v>
       </c>
       <c r="AR22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS22" t="n">
         <v>6</v>
@@ -4433,16 +4500,16 @@
         <v>24</v>
       </c>
       <c r="AV22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW22" t="n">
         <v>6</v>
       </c>
       <c r="AX22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ22" t="n">
         <v>18</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -4483,61 +4550,61 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E23" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F23" t="n">
         <v>19</v>
       </c>
       <c r="G23" t="n">
-        <v>0.661</v>
+        <v>0.667</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="J23" t="n">
         <v>77.90000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.457</v>
+        <v>0.459</v>
       </c>
       <c r="L23" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="M23" t="n">
         <v>27.7</v>
       </c>
       <c r="N23" t="n">
-        <v>0.36</v>
+        <v>0.364</v>
       </c>
       <c r="O23" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="P23" t="n">
-        <v>27.3</v>
+        <v>27.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.722</v>
+        <v>0.723</v>
       </c>
       <c r="R23" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="S23" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="T23" t="n">
-        <v>43.4</v>
+        <v>43.2</v>
       </c>
       <c r="U23" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="V23" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W23" t="n">
         <v>6.5</v>
@@ -4546,7 +4613,7 @@
         <v>5.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Z23" t="n">
         <v>20.5</v>
@@ -4555,13 +4622,13 @@
         <v>22.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>100.8</v>
+        <v>101.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
         <v>3</v>
@@ -4582,7 +4649,7 @@
         <v>26</v>
       </c>
       <c r="AK23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4591,7 +4658,7 @@
         <v>1</v>
       </c>
       <c r="AN23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO23" t="n">
         <v>7</v>
@@ -4600,7 +4667,7 @@
         <v>3</v>
       </c>
       <c r="AQ23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR23" t="n">
         <v>27</v>
@@ -4609,31 +4676,31 @@
         <v>1</v>
       </c>
       <c r="AT23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU23" t="n">
         <v>27</v>
       </c>
       <c r="AV23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW23" t="n">
         <v>25</v>
       </c>
       <c r="AX23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY23" t="n">
         <v>1</v>
       </c>
       <c r="AZ23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA23" t="n">
         <v>2</v>
       </c>
       <c r="BB23" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BC23" t="n">
         <v>3</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -4668,13 +4735,13 @@
         <v>55</v>
       </c>
       <c r="E24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F24" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4</v>
+        <v>0.382</v>
       </c>
       <c r="H24" t="n">
         <v>48.4</v>
@@ -4683,43 +4750,43 @@
         <v>37.1</v>
       </c>
       <c r="J24" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K24" t="n">
         <v>0.453</v>
       </c>
       <c r="L24" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M24" t="n">
         <v>16.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0.343</v>
+        <v>0.342</v>
       </c>
       <c r="O24" t="n">
         <v>17.8</v>
       </c>
       <c r="P24" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.776</v>
+        <v>0.774</v>
       </c>
       <c r="R24" t="n">
         <v>11.7</v>
       </c>
       <c r="S24" t="n">
-        <v>30.4</v>
+        <v>30.1</v>
       </c>
       <c r="T24" t="n">
-        <v>42.1</v>
+        <v>41.8</v>
       </c>
       <c r="U24" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V24" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W24" t="n">
         <v>8.4</v>
@@ -4728,7 +4795,7 @@
         <v>5.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z24" t="n">
         <v>20.3</v>
@@ -4737,13 +4804,13 @@
         <v>19.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>97.59999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>-2.3</v>
+        <v>-2.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE24" t="n">
         <v>22</v>
@@ -4764,31 +4831,31 @@
         <v>16</v>
       </c>
       <c r="AK24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL24" t="n">
         <v>22</v>
       </c>
       <c r="AM24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AN24" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO24" t="n">
         <v>23</v>
       </c>
       <c r="AP24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AR24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS24" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT24" t="n">
         <v>16</v>
@@ -4797,13 +4864,13 @@
         <v>17</v>
       </c>
       <c r="AV24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW24" t="n">
         <v>4</v>
       </c>
       <c r="AX24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY24" t="n">
         <v>4</v>
@@ -4812,10 +4879,10 @@
         <v>11</v>
       </c>
       <c r="BA24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC24" t="n">
         <v>21</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -4877,28 +4944,28 @@
         <v>21.8</v>
       </c>
       <c r="N25" t="n">
-        <v>0.402</v>
+        <v>0.401</v>
       </c>
       <c r="O25" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="P25" t="n">
         <v>25.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.77</v>
+        <v>0.772</v>
       </c>
       <c r="R25" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S25" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="T25" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="U25" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="V25" t="n">
         <v>15</v>
@@ -4919,7 +4986,7 @@
         <v>21.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>109.1</v>
+        <v>109.2</v>
       </c>
       <c r="AC25" t="n">
         <v>2.7</v>
@@ -4928,13 +4995,13 @@
         <v>2</v>
       </c>
       <c r="AE25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF25" t="n">
         <v>10</v>
       </c>
       <c r="AG25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH25" t="n">
         <v>26</v>
@@ -4946,7 +5013,7 @@
         <v>12</v>
       </c>
       <c r="AK25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL25" t="n">
         <v>3</v>
@@ -4964,13 +5031,13 @@
         <v>12</v>
       </c>
       <c r="AQ25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT25" t="n">
         <v>10</v>
@@ -4991,10 +5058,10 @@
         <v>10</v>
       </c>
       <c r="AZ25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB25" t="n">
         <v>1</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -5044,22 +5111,22 @@
         <v>48.5</v>
       </c>
       <c r="I26" t="n">
-        <v>35.9</v>
+        <v>35.7</v>
       </c>
       <c r="J26" t="n">
-        <v>77.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="K26" t="n">
-        <v>0.462</v>
+        <v>0.46</v>
       </c>
       <c r="L26" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="M26" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0.349</v>
+        <v>0.352</v>
       </c>
       <c r="O26" t="n">
         <v>19.5</v>
@@ -5068,40 +5135,40 @@
         <v>24.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.784</v>
+        <v>0.786</v>
       </c>
       <c r="R26" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S26" t="n">
-        <v>29.1</v>
+        <v>29.4</v>
       </c>
       <c r="T26" t="n">
-        <v>39.9</v>
+        <v>40.2</v>
       </c>
       <c r="U26" t="n">
         <v>20.2</v>
       </c>
       <c r="V26" t="n">
-        <v>12.7</v>
+        <v>13.1</v>
       </c>
       <c r="W26" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="X26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y26" t="n">
         <v>4</v>
       </c>
-      <c r="Y26" t="n">
-        <v>3.9</v>
-      </c>
       <c r="Z26" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.3</v>
+        <v>97.2</v>
       </c>
       <c r="AC26" t="n">
         <v>2.1</v>
@@ -5110,7 +5177,7 @@
         <v>1</v>
       </c>
       <c r="AE26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF26" t="n">
         <v>13</v>
@@ -5137,7 +5204,7 @@
         <v>16</v>
       </c>
       <c r="AN26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO26" t="n">
         <v>8</v>
@@ -5146,10 +5213,10 @@
         <v>13</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AS26" t="n">
         <v>28</v>
@@ -5161,7 +5228,7 @@
         <v>21</v>
       </c>
       <c r="AV26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW26" t="n">
         <v>28</v>
@@ -5170,7 +5237,7 @@
         <v>26</v>
       </c>
       <c r="AY26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ26" t="n">
         <v>19</v>
@@ -5182,7 +5249,7 @@
         <v>24</v>
       </c>
       <c r="BC26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -5229,19 +5296,19 @@
         <v>38.2</v>
       </c>
       <c r="J27" t="n">
-        <v>83.8</v>
+        <v>84</v>
       </c>
       <c r="K27" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L27" t="n">
         <v>6.4</v>
       </c>
       <c r="M27" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0.352</v>
+        <v>0.35</v>
       </c>
       <c r="O27" t="n">
         <v>18.4</v>
@@ -5250,7 +5317,7 @@
         <v>25.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.729</v>
+        <v>0.73</v>
       </c>
       <c r="R27" t="n">
         <v>12.2</v>
@@ -5262,7 +5329,7 @@
         <v>42.8</v>
       </c>
       <c r="U27" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V27" t="n">
         <v>15.7</v>
@@ -5271,16 +5338,16 @@
         <v>6.9</v>
       </c>
       <c r="X27" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB27" t="n">
         <v>101.2</v>
@@ -5289,7 +5356,7 @@
         <v>-4.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE27" t="n">
         <v>27</v>
@@ -5307,19 +5374,19 @@
         <v>8</v>
       </c>
       <c r="AJ27" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AK27" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AL27" t="n">
         <v>14</v>
       </c>
       <c r="AM27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AO27" t="n">
         <v>17</v>
@@ -5334,19 +5401,19 @@
         <v>4</v>
       </c>
       <c r="AS27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV27" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AW27" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AX27" t="n">
         <v>22</v>
@@ -5361,10 +5428,10 @@
         <v>15</v>
       </c>
       <c r="BB27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -5393,34 +5460,34 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E28" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F28" t="n">
         <v>23</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.574</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
       </c>
       <c r="I28" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J28" t="n">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K28" t="n">
-        <v>0.468</v>
+        <v>0.469</v>
       </c>
       <c r="L28" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="M28" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="N28" t="n">
         <v>0.364</v>
@@ -5429,31 +5496,31 @@
         <v>17.8</v>
       </c>
       <c r="P28" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.743</v>
+        <v>0.742</v>
       </c>
       <c r="R28" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S28" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="T28" t="n">
         <v>42.3</v>
       </c>
       <c r="U28" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="V28" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="W28" t="n">
         <v>6.4</v>
       </c>
       <c r="X28" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y28" t="n">
         <v>5.5</v>
@@ -5465,10 +5532,10 @@
         <v>20.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>100.3</v>
+        <v>100.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AD28" t="n">
         <v>27</v>
@@ -5486,43 +5553,43 @@
         <v>17</v>
       </c>
       <c r="AI28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ28" t="n">
         <v>17</v>
       </c>
       <c r="AK28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL28" t="n">
         <v>9</v>
       </c>
-      <c r="AL28" t="n">
-        <v>12</v>
-      </c>
       <c r="AM28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AN28" t="n">
         <v>5</v>
       </c>
       <c r="AO28" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AP28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ28" t="n">
         <v>20</v>
       </c>
       <c r="AR28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
         <v>12</v>
       </c>
       <c r="AU28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV28" t="n">
         <v>9</v>
@@ -5531,16 +5598,16 @@
         <v>26</v>
       </c>
       <c r="AX28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY28" t="n">
         <v>23</v>
       </c>
       <c r="AZ28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB28" t="n">
         <v>15</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -5575,28 +5642,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E29" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F29" t="n">
         <v>24</v>
       </c>
       <c r="G29" t="n">
-        <v>0.556</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H29" t="n">
         <v>48.2</v>
       </c>
       <c r="I29" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="J29" t="n">
-        <v>80.3</v>
+        <v>80.2</v>
       </c>
       <c r="K29" t="n">
-        <v>0.48</v>
+        <v>0.479</v>
       </c>
       <c r="L29" t="n">
         <v>6.5</v>
@@ -5605,25 +5672,25 @@
         <v>17.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0.376</v>
+        <v>0.375</v>
       </c>
       <c r="O29" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="P29" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="Q29" t="n">
         <v>0.766</v>
       </c>
       <c r="R29" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S29" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="T29" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="U29" t="n">
         <v>21.8</v>
@@ -5635,25 +5702,25 @@
         <v>5.6</v>
       </c>
       <c r="X29" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB29" t="n">
         <v>104.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AE29" t="n">
         <v>12</v>
@@ -5668,7 +5735,7 @@
         <v>23</v>
       </c>
       <c r="AI29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ29" t="n">
         <v>21</v>
@@ -5698,13 +5765,13 @@
         <v>25</v>
       </c>
       <c r="AS29" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AT29" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AU29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV29" t="n">
         <v>7</v>
@@ -5713,10 +5780,10 @@
         <v>30</v>
       </c>
       <c r="AX29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ29" t="n">
         <v>24</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -5757,22 +5824,22 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E30" t="n">
         <v>36</v>
       </c>
       <c r="F30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G30" t="n">
-        <v>0.655</v>
+        <v>0.643</v>
       </c>
       <c r="H30" t="n">
         <v>48.2</v>
       </c>
       <c r="I30" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="J30" t="n">
         <v>78.90000000000001</v>
@@ -5784,19 +5851,19 @@
         <v>4.6</v>
       </c>
       <c r="M30" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0.342</v>
+        <v>0.345</v>
       </c>
       <c r="O30" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="P30" t="n">
         <v>27</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.738</v>
+        <v>0.74</v>
       </c>
       <c r="R30" t="n">
         <v>10.1</v>
@@ -5805,7 +5872,7 @@
         <v>31</v>
       </c>
       <c r="T30" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="U30" t="n">
         <v>26.2</v>
@@ -5814,7 +5881,7 @@
         <v>15.2</v>
       </c>
       <c r="W30" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X30" t="n">
         <v>5.1</v>
@@ -5823,7 +5890,7 @@
         <v>5.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AA30" t="n">
         <v>22.3</v>
@@ -5832,22 +5899,22 @@
         <v>101.9</v>
       </c>
       <c r="AC30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE30" t="n">
         <v>5</v>
       </c>
-      <c r="AD30" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>4</v>
-      </c>
       <c r="AF30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AG30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AH30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI30" t="n">
         <v>5</v>
@@ -5859,13 +5926,13 @@
         <v>1</v>
       </c>
       <c r="AL30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM30" t="n">
         <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO30" t="n">
         <v>5</v>
@@ -5874,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="AQ30" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AR30" t="n">
         <v>24</v>
@@ -5883,34 +5950,34 @@
         <v>12</v>
       </c>
       <c r="AT30" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW30" t="n">
         <v>5</v>
       </c>
       <c r="AX30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ30" t="n">
         <v>23</v>
       </c>
       <c r="BA30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F31" t="n">
         <v>34</v>
       </c>
       <c r="G31" t="n">
-        <v>0.358</v>
+        <v>0.37</v>
       </c>
       <c r="H31" t="n">
         <v>48.4</v>
@@ -5972,28 +6039,28 @@
         <v>0.347</v>
       </c>
       <c r="O31" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P31" t="n">
         <v>24.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.766</v>
+        <v>0.768</v>
       </c>
       <c r="R31" t="n">
         <v>11.9</v>
       </c>
       <c r="S31" t="n">
-        <v>30.2</v>
+        <v>30.4</v>
       </c>
       <c r="T31" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U31" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="V31" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W31" t="n">
         <v>6.4</v>
@@ -6005,34 +6072,34 @@
         <v>4.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="AA31" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>97.90000000000001</v>
+        <v>98</v>
       </c>
       <c r="AC31" t="n">
-        <v>-3.8</v>
+        <v>-3.6</v>
       </c>
       <c r="AD31" t="n">
         <v>27</v>
       </c>
       <c r="AE31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG31" t="n">
         <v>23</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>24</v>
       </c>
       <c r="AH31" t="n">
         <v>12</v>
       </c>
       <c r="AI31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="n">
         <v>14</v>
@@ -6047,13 +6114,13 @@
         <v>21</v>
       </c>
       <c r="AN31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO31" t="n">
         <v>16</v>
       </c>
       <c r="AP31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ31" t="n">
         <v>13</v>
@@ -6062,22 +6129,22 @@
         <v>8</v>
       </c>
       <c r="AS31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU31" t="n">
         <v>29</v>
       </c>
       <c r="AV31" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY31" t="n">
         <v>14</v>
@@ -6086,7 +6153,7 @@
         <v>20</v>
       </c>
       <c r="BA31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB31" t="n">
         <v>20</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-23-2009-10</t>
+          <t>2010-02-23</t>
         </is>
       </c>
     </row>
